--- a/Indomie Clients Details/lmt orders 12-06.xlsx
+++ b/Indomie Clients Details/lmt orders 12-06.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED77823C-119A-4C55-A9F5-B34517333E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5E927E4-25DC-4DA6-AECC-7FEF68402528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" r:id="rId1"/>

--- a/Indomie Clients Details/lmt orders 12-06.xlsx
+++ b/Indomie Clients Details/lmt orders 12-06.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B75D1E1-A4B2-4C40-9E6E-2B903B18927B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5B46E1F-DB2F-4CBD-B5BE-588C6014D194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" r:id="rId1"/>
@@ -3394,7 +3394,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -3422,7 +3422,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -4626,7 +4626,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -4654,7 +4654,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -5847,7 +5847,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -5875,7 +5875,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -7068,7 +7068,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -7096,7 +7096,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -8289,7 +8289,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -8317,7 +8317,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -9510,7 +9510,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -9538,7 +9538,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -10728,7 +10728,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -10756,7 +10756,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -11945,7 +11945,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -11973,7 +11973,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -13162,7 +13162,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -13190,7 +13190,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -14379,7 +14379,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -14407,7 +14407,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -18346,7 +18346,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -18374,7 +18374,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -19563,7 +19563,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -19591,7 +19591,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -20780,7 +20780,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -20808,7 +20808,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -21997,7 +21997,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -22025,7 +22025,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -23219,7 +23219,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -23247,7 +23247,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -24711,7 +24711,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -24739,7 +24739,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -25960,7 +25960,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -25988,7 +25988,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -27195,7 +27195,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -27223,7 +27223,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -28426,7 +28426,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -28454,7 +28454,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -29662,7 +29662,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -29690,7 +29690,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -30891,7 +30891,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -30919,7 +30919,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
